--- a/tiflow-chargeitem/main/2.0.0-ballot.2/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/main/2.0.0-ballot.2/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:39:26+00:00</t>
+    <t>2026-07-23T13:24:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
